--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
   <si>
     <t>ID</t>
   </si>
@@ -131,63 +131,63 @@
     <t>恶魔先锋</t>
   </si>
   <si>
-    <t>10000</t>
+    <t>5000</t>
   </si>
   <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>5E+6</t>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1E+5</t>
   </si>
   <si>
     <t>1.2</t>
   </si>
   <si>
-    <t>1000</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
     <t>恶魔步兵</t>
   </si>
   <si>
-    <t>100000</t>
-  </si>
-  <si>
-    <t>20000</t>
-  </si>
-  <si>
-    <t>4E+8</t>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>10E+6</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>恶魔骑兵</t>
+  </si>
+  <si>
+    <t>1850000</t>
+  </si>
+  <si>
+    <t>370000</t>
+  </si>
+  <si>
+    <t>2.7E+9</t>
   </si>
   <si>
     <t>1.3</t>
   </si>
   <si>
-    <t>4000</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>恶魔骑兵</t>
-  </si>
-  <si>
-    <t>8000000</t>
-  </si>
-  <si>
-    <t>1600000</t>
-  </si>
-  <si>
-    <t>22E+10</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
     <t>15000</t>
   </si>
   <si>
@@ -197,22 +197,19 @@
     <t>恶魔禁卫</t>
   </si>
   <si>
-    <t>4400000000</t>
-  </si>
-  <si>
-    <t>880000000</t>
-  </si>
-  <si>
-    <t>77E+13</t>
-  </si>
-  <si>
-    <t>1.5</t>
+    <t>18E+7</t>
+  </si>
+  <si>
+    <t>36E+6</t>
+  </si>
+  <si>
+    <t>2E+12</t>
+  </si>
+  <si>
+    <t>1.35</t>
   </si>
   <si>
     <t>50000</t>
-  </si>
-  <si>
-    <t>5000</t>
   </si>
   <si>
     <t>#</t>
@@ -1611,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD6" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="AD6" s="7" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="1:30">
@@ -1622,7 +1619,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1634,16 +1631,16 @@
         <v>50</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>42</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>43</v>
@@ -1723,13 +1720,13 @@
         <v>48</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>50</v>
@@ -1809,13 +1806,13 @@
         <v>55</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>56</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>57</v>
@@ -1872,7 +1869,7 @@
         <v>59</v>
       </c>
       <c r="AD9" s="7" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:30">
@@ -1888,16 +1885,16 @@
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2">
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
@@ -1909,22 +1906,22 @@
         <v>25</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="M11" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N11" s="2">
         <v>0</v>
@@ -1963,24 +1960,24 @@
         <v>0</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2">
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2">
         <v>2</v>
@@ -1992,22 +1989,22 @@
         <v>50</v>
       </c>
       <c r="H12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="M12" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N12" s="2">
         <v>0</v>
@@ -2046,24 +2043,24 @@
         <v>0</v>
       </c>
       <c r="AC12" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AD12" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2">
         <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2">
         <v>2</v>
@@ -2075,22 +2072,22 @@
         <v>75</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="M13" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N13" s="2">
         <v>0</v>
@@ -2129,24 +2126,24 @@
         <v>0</v>
       </c>
       <c r="AC13" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AD13" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="1:30">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2">
         <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -2158,22 +2155,22 @@
         <v>100</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="6" t="s">
+      <c r="K14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="M14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N14" s="2">
         <v>0</v>
@@ -2212,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="AC14" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AD14" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="1:30">
@@ -2230,7 +2227,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:O5 P5 Q5 R5:Y5 Z5:AB5 C3:O4 R3:Y4 P3:Q4 Z3:AB4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AB5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
